--- a/input_courses/材料成型技术_2025-2026-1/02_学生成绩表.xlsx
+++ b/input_courses/材料成型技术_2025-2026-1/02_学生成绩表.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K121"/>
+  <dimension ref="A1:L121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,6 +484,11 @@
           <t>所属学期</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>数据来源说明</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -529,6 +534,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -574,6 +584,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -619,6 +634,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -664,6 +684,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -709,6 +734,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -754,6 +784,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -799,6 +834,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -844,6 +884,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -889,6 +934,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -934,6 +984,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -979,6 +1034,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1024,6 +1084,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1069,6 +1134,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1114,6 +1184,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1159,6 +1234,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1204,6 +1284,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1249,6 +1334,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1294,6 +1384,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1339,6 +1434,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1384,6 +1484,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1429,6 +1534,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1474,6 +1584,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1519,6 +1634,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1564,6 +1684,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1609,6 +1734,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1654,6 +1784,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1699,6 +1834,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1744,6 +1884,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1789,6 +1934,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1834,6 +1984,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1879,6 +2034,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1924,6 +2084,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1969,6 +2134,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2014,6 +2184,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2059,6 +2234,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2104,6 +2284,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2149,6 +2334,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2194,6 +2384,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2239,6 +2434,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2284,6 +2484,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2329,6 +2534,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2374,6 +2584,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2419,6 +2634,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2464,6 +2684,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2509,6 +2734,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2554,6 +2784,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2599,6 +2834,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2644,6 +2884,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2689,6 +2934,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2734,6 +2984,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2779,6 +3034,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2824,6 +3084,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2869,6 +3134,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2914,6 +3184,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2959,6 +3234,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3004,6 +3284,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3049,6 +3334,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3094,6 +3384,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3139,6 +3434,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3184,6 +3484,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3229,6 +3534,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3274,6 +3584,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3319,6 +3634,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3364,6 +3684,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3409,6 +3734,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3454,6 +3784,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3499,6 +3834,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3544,6 +3884,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3589,6 +3934,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3634,6 +3984,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3679,6 +4034,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3724,6 +4084,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3769,6 +4134,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3814,6 +4184,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3859,6 +4234,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3904,6 +4284,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3949,6 +4334,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3994,6 +4384,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4039,6 +4434,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4084,6 +4484,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4129,6 +4534,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4174,6 +4584,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4219,6 +4634,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4264,6 +4684,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4309,6 +4734,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4354,6 +4784,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4399,6 +4834,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4444,6 +4884,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4489,6 +4934,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4534,6 +4984,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4579,6 +5034,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4624,6 +5084,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4669,6 +5134,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4714,6 +5184,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4759,6 +5234,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4804,6 +5284,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4849,6 +5334,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4894,6 +5384,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4939,6 +5434,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4984,6 +5484,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5029,6 +5534,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5074,6 +5584,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5119,6 +5634,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5164,6 +5684,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5209,6 +5734,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5254,6 +5784,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5299,6 +5834,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -5344,6 +5884,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -5389,6 +5934,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -5434,6 +5984,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5479,6 +6034,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5524,6 +6084,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -5569,6 +6134,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5614,6 +6184,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -5659,6 +6234,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -5704,6 +6284,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -5749,6 +6334,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -5794,6 +6384,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -5839,6 +6434,11 @@
           <t>2025-2026第一学期</t>
         </is>
       </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -5882,6 +6482,11 @@
       <c r="K121" t="inlineStr">
         <is>
           <t>2025-2026第一学期</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>真实分项成绩</t>
         </is>
       </c>
     </row>
